--- a/mock/raw/PFMEA01.xlsx
+++ b/mock/raw/PFMEA01.xlsx
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
+      <c r="C34" s="7" t="n"/>
       <c r="D34" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -2038,7 +2038,11 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="7" t="n"/>
       <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>프리 실링</t>
+        </is>
+      </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -2088,6 +2092,7 @@
     <mergeCell ref="G17:G18"/>
     <mergeCell ref="G8:G9"/>
     <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C33:C34"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="H21:H22"/>
@@ -2105,7 +2110,6 @@
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="C21:C24"/>
     <mergeCell ref="C31:C32"/>
-    <mergeCell ref="C33:C35"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="C17:C20"/>
